--- a/data/trans_camb/IP1009-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,0</t>
+          <t>-3,99; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,53</t>
+          <t>-1,97; 2,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,0</t>
+          <t>-4,82; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,0</t>
+          <t>-5,38; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; -0,22</t>
+          <t>-2,51; -0,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,82</t>
+          <t>-1,75; 1,03</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,3</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
     </row>
@@ -953,17 +953,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,0</t>
+          <t>-3,53; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 0,0</t>
+          <t>-3,54; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,0</t>
+          <t>-2,09; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,4</t>
+          <t>0,1; 1,17</t>
         </is>
       </c>
     </row>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,0</t>
+          <t>-2,75; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,0</t>
+          <t>-3,04; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,0</t>
+          <t>-1,51; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,97</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,84</t>
+          <t>0,0; 5,3</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>0,0; 3,79</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,45</t>
+          <t>-0,33; 0,39</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,78</t>
+          <t>-0,18; 0,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,09</t>
+          <t>-0,71; 0,08</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,67</t>
+          <t>-0,41; 0,59</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,14</t>
+          <t>-0,42; 0,14</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,49</t>
+          <t>-0,18; 0,5</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1658,17 +1658,17 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-86,35; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 221,58</t>
+          <t>-100,0; 301,7</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-52,58; 488,3</t>
+          <t>-62,22; 695,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1009-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 0,0</t>
+          <t>-4,04; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 2,72</t>
+          <t>-2,24; 2,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 0,0</t>
+          <t>-3,49; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 0,0</t>
+          <t>-3,02; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; -0,22</t>
+          <t>-2,28; -0,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,03</t>
+          <t>-1,67; 0,83</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>0,0; 3,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,0</t>
+          <t>-4,18; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 0,0</t>
+          <t>-4,17; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,0</t>
+          <t>-1,98; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,0</t>
+          <t>-2,07; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,17</t>
+          <t>0,1; 1,08</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,0</t>
+          <t>-2,66; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,0</t>
+          <t>-1,69; 0,0</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,12</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,3</t>
+          <t>0,0; 5,28</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,79</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,39</t>
+          <t>-0,34; 0,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,77</t>
+          <t>-0,18; 0,8</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,08</t>
+          <t>-0,7; 0,09</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,59</t>
+          <t>-0,41; 0,61</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,14</t>
+          <t>-0,43; 0,14</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,5</t>
+          <t>-0,19; 0,46</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-86,35; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 301,7</t>
+          <t>-100,0; 257,18</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-62,22; 695,34</t>
+          <t>-59,02; 502,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1009-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-1,04</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,13</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,0</t>
+          <t>-3,26; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,42</t>
+          <t>-3,49; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,0</t>
+          <t>-3,74; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 0,0</t>
+          <t>-2,05; 2,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; -0,22</t>
+          <t>-2,4; -0,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,83</t>
+          <t>-1,73; 0,82</t>
         </is>
       </c>
     </row>
@@ -674,17 +674,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-12,57%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,24</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,69</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 3,4</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,7</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,47; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,51; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,0</t>
+          <t>-2,38; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,0</t>
+          <t>-2,1; 0,0</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,55</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,08</t>
+          <t>0,1; 1,4</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,55</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,55</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,78; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,66; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>-1,86; 0,0</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>-1,51; 0,0</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-1,69; 0,0</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1378,17 +1378,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>1,06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>0,99</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 5,84</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,28</t>
+          <t>0,0; 4,97</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,37</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,22</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,02</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>0,22</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,22</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,41</t>
+          <t>-0,62; 0,09</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,8</t>
+          <t>-0,41; 0,67</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,09</t>
+          <t>-0,3; 0,45</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,61</t>
+          <t>-0,16; 0,78</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,14</t>
+          <t>-0,4; 0,14</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,46</t>
+          <t>-0,16; 0,49</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-71,31%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>25,82%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>14,17%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>127,38%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-71,31%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>25,82%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1658,17 +1658,17 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 257,18</t>
+          <t>-100,0; 221,58</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-59,02; 502,26</t>
+          <t>-52,58; 488,3</t>
         </is>
       </c>
     </row>
